--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0209.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0209.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>"ÔI, THÔI NÀO! Ngươi... Ta chỉ mong ngươi đừng biến thành một trong những kẻ người lớn nhàm chán ấy thôi."</t>
+          <t>"ÔI, THÔI NÀO! Mày... Tao chỉ mong mày đừng biến thành một trong những kẻ người lớn nhàm chán ấy thôi."</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>"Ý nghĩa của tất cả những gì ngươi làm là gì nếu ngươi không dám lên tiếng?! Ta phải nhắc lại lời thề ngày chúng ta lập ban nhạc à?!"</t>
+          <t>"Ý nghĩa của tất cả những gì mày làm là gì nếu mày không dám lên tiếng?! Tao phải nhắc lại lời thề ngày chúng ta lập ban nhạc à?!"</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>"Ê! Đồ quái gì thế?! Tại sao lại đánh ta?!"</t>
+          <t>"Ê! Đồ quái gì thế?! Tại sao lại đánh tao?!"</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Tăng Trạng Thái] Ta đến vì kho báu.</t>
+          <t>Tăng Trạng Thái] Tao đến vì kho báu.</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>"Ừ! Ngươi nhận tiền rồi chuồn thẳng. Đó là lý do ta thành kẻ cướp giờ đây! Còn mẹ ta, bà vẫn mắc kẹt trong thị trấn! Bà không chạy nhanh như ngươi được, chân bà đau mà!"</t>
+          <t>"Ừ! Mày nhận tiền rồi chuồn thẳng. Đó là lý do tao thành kẻ cướp giờ đây! Còn mẹ tao, bà vẫn mắc kẹt trong thị trấn! Bà không chạy nhanh như mày được, chân bà đau mà!"</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>"Ê... Ê ê... Đầu ta đau quá. Cậu nói lại mấy cái đó kiểu dễ hiểu hơn được không?"</t>
+          <t>"Ê... Ê ê... Đầu tao đau quá. Cậu nói lại mấy cái đó kiểu dễ hiểu hơn được không?"</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>"Trời ơi, {PlayerName}. Từng chữ thì ta hiểu, nhưng ghép lại thì chẳng hiểu mô tê gì cả!"</t>
+          <t>"Trời ơi, {PlayerName}. Từng chữ thì tao hiểu, nhưng ghép lại thì chẳng hiểu mô tê gì cả!"</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>"Ừ! Mấy lời hoa mỹ của cậu bay qua đầu ta luôn. Nhưng ngay từ đầu, mọi người trong phim này đã hành động kỳ lạ hơn bình thường rồi. Chết thật!"</t>
+          <t>"Ừ! Mấy lời hoa mỹ của cậu bay qua đầu tao luôn. Nhưng ngay từ đầu, mọi người trong phim này đã hành động kỳ lạ hơn bình thường rồi. Chết thật!"</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>"Dù vậy, ta không ngờ người được chọn lại trẻ đến thế... Cậu có hiểu lời hứa này đòi hỏi điều gì không?"</t>
+          <t>"Dù vậy, tao không ngờ người được chọn lại trẻ đến thế... Cậu có hiểu lời hứa này đòi hỏi điều gì không?"</t>
         </is>
       </c>
     </row>
@@ -20464,7 +20464,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>"Ra vậy. Ta nghe nói về tình hình bất ổn ở Vùng Biên Giới. Không ngờ ngọn núi thiêng này cũng dính vào vòng xoáy."</t>
+          <t>"Ra vậy. Tao nghe nói về tình hình bất ổn ở Vùng Biên Giới. Không ngờ ngọn núi thiêng này cũng dính vào vòng xoáy."</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>"C-Có vấn đề gì không? Đồ ăn là tất cả! Ta đang đói muốn chết đây! Chạy vòng vòng khắp nơi mãi..."</t>
+          <t>"C-Có vấn đề gì không? Đồ ăn là tất cả! Tao đang đói muốn chết đây! Chạy vòng vòng khắp nơi mãi..."</t>
         </is>
       </c>
     </row>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>"...Chẳng thằng nào là đối thủ của ta cả. Dĩ nhiên... nếu cậu có thể chia cho ta vài cái Bánh Mì Dẹt, ta sẽ mang ơn suốt đời..."</t>
+          <t>"...Chẳng thằng nào là đối thủ của tao cả. Dĩ nhiên... nếu cậu có thể chia cho tao vài cái Bánh Mì Dẹt, tao sẽ mang ơn suốt đời..."</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>"Đồ phế liệu núi thối thế này?! Ta với ngươi còng lưng vác về đây cơ mà! Đồ nhãi ranh! Thế này là đủ rồi, đến lúc dạy cho ngươi bài học!"</t>
+          <t>"Đồ phế liệu núi thối thế này?! Tao với mày còng lưng vác về đây cơ mà! Đồ nhãi ranh! Thế này là đủ rồi, đến lúc dạy cho mày bài học!"</t>
         </is>
       </c>
     </row>
@@ -23064,7 +23064,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>"Vậy là ngươi có đồng bọn à? Chúng ta đã bị lộ rồi. Lên súng, anh em! Hôm nay không ai trong hai đứa được rời khỏi đây sống đâu!"</t>
+          <t>"Vậy là mày có đồng bọn à? Chúng ta đã bị lộ rồi. Lên súng, anh em! Hôm nay không ai trong hai đứa được rời khỏi đây sống đâu!"</t>
         </is>
       </c>
     </row>
@@ -23844,7 +23844,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>"Ngôn ngữ gì mà kỳ vậy? Ta chẳng hiểu nổi một chữ... Nhảm nhí. Ờ."</t>
+          <t>"Ngôn ngữ gì mà kỳ vậy? Tao chẳng hiểu nổi một chữ... Nhảm nhí. Ờ."</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Gia nhập cùng cậu à? Nghe như lời mời làm việc chui... nhưng thôi, nếu là vì đứa trẻ đó, ta sẽ đi cùng.</t>
+          <t>Gia nhập cùng cậu à? Nghe như lời mời làm việc chui... nhưng thôi, nếu là vì đứa trẻ đó, tao sẽ đi cùng.</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>"Này, thoải mái đi, {PlayerName}! Lại đây tắm suối nước nóng với ta nào. Chắc chẳng còn nơi nào như thế này nữa đâu."</t>
+          <t>"Này, thoải mái đi, {PlayerName}! Lại đây tắm suối nước nóng với tao nào. Chắc chẳng còn nơi nào như thế này nữa đâu."</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>"Cậu là người ở quán trọ phải không? Ta nhớ rõ tài nghệ của cậu... Nếu lúc đó cậu chiến đấu cùng chúng ta... có lẽ chúng ta đã thắng rồi..."</t>
+          <t>"Cậu là người ở quán trọ phải không? Tao nhớ rõ tài nghệ của cậu... Nếu lúc đó cậu chiến đấu cùng chúng tao... có lẽ chúng tao đã thắng rồi..."</t>
         </is>
       </c>
     </row>
@@ -29304,7 +29304,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Tăng Trạng Thái] Ta cần vài đồ tiếp tế.</t>
+          <t>Tăng Trạng Thái] Tao cần vài đồ tiếp tế.</t>
         </is>
       </c>
     </row>
@@ -31645,7 +31645,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Sự dứt khoát trong lời hắn khiến cậu bối rối. Ai đã ra lệnh bắt? Chúng muốn gì ở cậu chứ?</t>
+          <t>Sự dứt khoát trong lời hắn khiến mày bối rối. Ai đã ra lệnh bắt? Chúng muốn gì ở mày chứ?</t>
         </is>
       </c>
     </row>
